--- a/GameConfig/Datas/Defines/__enums__.xlsx
+++ b/GameConfig/Datas/Defines/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87472CDF-E254-405E-9365-484244C14B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="8"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="1" r:id="rId1"/>
@@ -16,6 +22,7 @@
     <sheet name="活动类型枚举" sheetId="8" r:id="rId7"/>
     <sheet name="系统开放类型" sheetId="9" r:id="rId8"/>
     <sheet name="怪物类型" sheetId="11" r:id="rId9"/>
+    <sheet name="新手引导" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="228">
   <si>
     <t>##var</t>
   </si>
@@ -446,19 +453,286 @@
   </si>
   <si>
     <t>Boss</t>
+  </si>
+  <si>
+    <t>EGuideType</t>
+  </si>
+  <si>
+    <t>引导类型</t>
+  </si>
+  <si>
+    <t>ForceGuide</t>
+  </si>
+  <si>
+    <t>强引导</t>
+  </si>
+  <si>
+    <t>WeakGuide</t>
+  </si>
+  <si>
+    <t>弱引导</t>
+  </si>
+  <si>
+    <t>EGuideState</t>
+  </si>
+  <si>
+    <t>引导运行状态</t>
+  </si>
+  <si>
+    <t>NotReady</t>
+  </si>
+  <si>
+    <t>未就绪</t>
+  </si>
+  <si>
+    <t>Idle</t>
+  </si>
+  <si>
+    <t>空闲</t>
+  </si>
+  <si>
+    <t>ResolvingTarget</t>
+  </si>
+  <si>
+    <t>解析目标</t>
+  </si>
+  <si>
+    <t>Presenting</t>
+  </si>
+  <si>
+    <t>展示中</t>
+  </si>
+  <si>
+    <t>Waiting</t>
+  </si>
+  <si>
+    <t>等待中</t>
+  </si>
+  <si>
+    <t>Paused</t>
+  </si>
+  <si>
+    <t>已暂停</t>
+  </si>
+  <si>
+    <t>EGuideStepType</t>
+  </si>
+  <si>
+    <t>引导步骤类型</t>
+  </si>
+  <si>
+    <t>Explain</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>ClickTarget</t>
+  </si>
+  <si>
+    <t>点击目标</t>
+  </si>
+  <si>
+    <t>ClickAnywhere</t>
+  </si>
+  <si>
+    <t>任意点击</t>
+  </si>
+  <si>
+    <t>WaitEvent</t>
+  </si>
+  <si>
+    <t>等待事件</t>
+  </si>
+  <si>
+    <t>Delay</t>
+  </si>
+  <si>
+    <t>延时</t>
+  </si>
+  <si>
+    <t>DragHint</t>
+  </si>
+  <si>
+    <t>拖拽提示</t>
+  </si>
+  <si>
+    <t>CustomAction</t>
+  </si>
+  <si>
+    <t>自定义动作</t>
+  </si>
+  <si>
+    <t>EGuideInputMode</t>
+  </si>
+  <si>
+    <t>引导输入模式</t>
+  </si>
+  <si>
+    <t>BlockAll</t>
+  </si>
+  <si>
+    <t>全部拦截</t>
+  </si>
+  <si>
+    <t>PassThroughTarget</t>
+  </si>
+  <si>
+    <t>目标透传</t>
+  </si>
+  <si>
+    <t>AllowAll</t>
+  </si>
+  <si>
+    <t>全部放行</t>
+  </si>
+  <si>
+    <t>EGuideSkipScope</t>
+  </si>
+  <si>
+    <t>引导跳过范围</t>
+  </si>
+  <si>
+    <t>Guide</t>
+  </si>
+  <si>
+    <t>当前引导</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>整个引导组</t>
+  </si>
+  <si>
+    <t>EGuideResumePolicy</t>
+  </si>
+  <si>
+    <t>引导恢复策略</t>
+  </si>
+  <si>
+    <t>RestartGuide</t>
+  </si>
+  <si>
+    <t>重启引导</t>
+  </si>
+  <si>
+    <t>ResumeStep</t>
+  </si>
+  <si>
+    <t>恢复步骤</t>
+  </si>
+  <si>
+    <t>DoNotResume</t>
+  </si>
+  <si>
+    <t>不恢复</t>
+  </si>
+  <si>
+    <t>EGuideFailurePolicy</t>
+  </si>
+  <si>
+    <t>引导故障策略</t>
+  </si>
+  <si>
+    <t>Retry</t>
+  </si>
+  <si>
+    <t>重试</t>
+  </si>
+  <si>
+    <t>SkipStep</t>
+  </si>
+  <si>
+    <t>跳过步骤</t>
+  </si>
+  <si>
+    <t>AbortGuide</t>
+  </si>
+  <si>
+    <t>中止引导</t>
+  </si>
+  <si>
+    <t>EGuideTipPlacement</t>
+  </si>
+  <si>
+    <t>引导提示位置</t>
+  </si>
+  <si>
+    <t>ScreenCenter</t>
+  </si>
+  <si>
+    <t>屏幕中央</t>
+  </si>
+  <si>
+    <t>AboveTarget</t>
+  </si>
+  <si>
+    <t>目标上方</t>
+  </si>
+  <si>
+    <t>BelowTarget</t>
+  </si>
+  <si>
+    <t>目标下方</t>
+  </si>
+  <si>
+    <t>EGuideMaskShape</t>
+  </si>
+  <si>
+    <t>引导遮罩形状，与GuideMask Shader的_MaskType直接对应</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>无遮罩孔</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>圆形</t>
+  </si>
+  <si>
+    <t>Rectangle</t>
+  </si>
+  <si>
+    <t>矩形</t>
+  </si>
+  <si>
+    <t>RoundedRectangle</t>
+  </si>
+  <si>
+    <t>圆角矩形</t>
+  </si>
+  <si>
+    <t>EGuideArrowMoveType</t>
+  </si>
+  <si>
+    <t>引导手指移动类型</t>
+  </si>
+  <si>
+    <t>不显示</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>中间移动到目标位置</t>
+  </si>
+  <si>
+    <t>CustomMove</t>
+  </si>
+  <si>
+    <t>自定义移动方向</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,151 +741,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -620,198 +756,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799890133365886"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -834,251 +784,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1095,62 +803,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1163,6 +844,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1420,29 +1104,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14.0833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="30" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="32.5833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.58203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="37.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.33333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="36.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1464,15 +1148,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1498,7 +1182,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1528,7 +1212,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1554,7 +1238,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="1" t="s">
         <v>23</v>
       </c>
@@ -1568,7 +1252,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1582,17 +1266,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>27</v>
       </c>
@@ -1618,7 +1302,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H10" s="1" t="s">
         <v>31</v>
       </c>
@@ -1632,7 +1316,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H11" s="1" t="s">
         <v>33</v>
       </c>
@@ -1646,7 +1330,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H12" s="1" t="s">
         <v>35</v>
       </c>
@@ -1660,7 +1344,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H13" s="1" t="s">
         <v>37</v>
       </c>
@@ -1674,7 +1358,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H14" s="1" t="s">
         <v>39</v>
       </c>
@@ -1688,7 +1372,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H15" s="1" t="s">
         <v>41</v>
       </c>
@@ -1702,7 +1386,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H16" s="1" t="s">
         <v>43</v>
       </c>
@@ -1716,7 +1400,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="8:11">
+    <row r="17" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H17" s="1" t="s">
         <v>45</v>
       </c>
@@ -1734,17 +1418,647 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16F9D4BE-B153-4673-9FB8-121FEB967091}">
+  <dimension ref="A1:L39"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="93.58203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="1"/>
+    <col min="6" max="6" width="8.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="51.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="168" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H5" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H9" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J9" s="1">
+        <v>3</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H10" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J10" s="1">
+        <v>4</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H11" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J11" s="1">
+        <v>5</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H13" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H14" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H15" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J15" s="1">
+        <v>3</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H16" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J16" s="1">
+        <v>4</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H17" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J17" s="1">
+        <v>5</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H18" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J18" s="1">
+        <v>6</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H20" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H21" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H23" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H25" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H26" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J26" s="1">
+        <v>2</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H28" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H29" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J29" s="1">
+        <v>2</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H31" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H32" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J32" s="1">
+        <v>2</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H34" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H35" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="J35" s="1">
+        <v>2</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H36" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="J36" s="1">
+        <v>3</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C37" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H38" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H39" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
@@ -1753,14 +2067,14 @@
     <col min="5" max="5" width="9" style="1"/>
     <col min="6" max="6" width="31" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="32.0833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.08203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="24.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.8333333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="27.0833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.08203125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1782,15 +2096,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1816,7 +2130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1846,7 +2160,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>47</v>
       </c>
@@ -1872,7 +2186,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="1" t="s">
         <v>51</v>
       </c>
@@ -1886,7 +2200,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" s="1" t="s">
         <v>53</v>
       </c>
@@ -1900,7 +2214,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="1" t="s">
         <v>55</v>
       </c>
@@ -1914,7 +2228,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H8" s="1" t="s">
         <v>57</v>
       </c>
@@ -1928,7 +2242,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H9" s="1" t="s">
         <v>59</v>
       </c>
@@ -1946,33 +2260,32 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="49.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="19.8333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
     <col min="8" max="8" width="21.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
     <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.3333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.75" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1994,15 +2307,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2028,7 +2341,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="57" spans="1:12">
+    <row r="3" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2058,8 +2371,8 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C4" s="1" t="b">
@@ -2071,24 +2384,24 @@
       <c r="F4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="J4" s="1">
         <v>1000001</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="H5" s="4" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H5" s="1" t="s">
         <v>65</v>
       </c>
       <c r="J5" s="1">
         <v>1000002</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2096,43 +2409,42 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D1048576" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="40.0833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.08203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="69.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="42.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="24" style="1" customWidth="1"/>
     <col min="10" max="10" width="14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.0833333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.08203125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2154,15 +2466,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2188,7 +2500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="28.5" spans="1:12">
+    <row r="3" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2218,8 +2530,8 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="1" t="b">
@@ -2231,62 +2543,57 @@
       <c r="F4" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="1" t="s">
         <v>70</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="H5" s="4"/>
-      <c r="K5" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H4:H5">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J5">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D5" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.66666666666667" style="1"/>
-    <col min="2" max="2" width="20.5833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.4166666666667" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.66666666666667" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.4140625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.6640625" style="1"/>
     <col min="6" max="6" width="27.5" style="1" customWidth="1"/>
-    <col min="7" max="8" width="8.66666666666667" style="1"/>
-    <col min="9" max="9" width="28.8333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.66666666666667" style="1"/>
+    <col min="7" max="8" width="8.6640625" style="1"/>
+    <col min="9" max="9" width="28.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="1"/>
     <col min="11" max="11" width="31.25" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.66666666666667" style="1"/>
+    <col min="12" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2308,15 +2615,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2342,7 +2649,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="85.5" spans="1:12">
+    <row r="3" spans="1:12" ht="84" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2372,8 +2679,8 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C4" s="1" t="b">
@@ -2385,34 +2692,34 @@
       <c r="F4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="1" t="s">
         <v>74</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="H5" s="4" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="1" t="s">
         <v>76</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" s="1" t="s">
         <v>77</v>
       </c>
@@ -2426,7 +2733,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="1" t="s">
         <v>79</v>
       </c>
@@ -2440,7 +2747,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H8" s="1" t="s">
         <v>81</v>
       </c>
@@ -2454,7 +2761,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H9" s="1" t="s">
         <v>83</v>
       </c>
@@ -2468,7 +2775,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H10" s="1" t="s">
         <v>85</v>
       </c>
@@ -2482,7 +2789,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H11" s="1" t="s">
         <v>87</v>
       </c>
@@ -2500,37 +2807,36 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D4" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.66666666666667" style="1"/>
-    <col min="2" max="2" width="25.4166666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.8333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.83333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="25.4140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="26.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.66666666666667" style="1"/>
-    <col min="8" max="8" width="56.1666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="1"/>
+    <col min="8" max="8" width="56.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="39.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.66666666666667" style="1"/>
-    <col min="11" max="11" width="44.3333333333333" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.66666666666667" style="1"/>
+    <col min="10" max="10" width="8.6640625" style="1"/>
+    <col min="11" max="11" width="44.33203125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2552,15 +2858,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2586,7 +2892,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="128.25" spans="1:12">
+    <row r="3" spans="1:12" ht="112" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2616,8 +2922,8 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C4" s="1" t="b">
@@ -2629,142 +2935,142 @@
       <c r="F4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="1" t="s">
         <v>92</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="H5" s="4" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H5" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="H6" s="4" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H6" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="1" t="s">
         <v>96</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="H7" s="4" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H7" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="1" t="s">
         <v>98</v>
       </c>
       <c r="J7" s="1">
         <v>3</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="H8" s="4" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H8" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="1" t="s">
         <v>100</v>
       </c>
       <c r="J8" s="1">
         <v>4</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="H9" s="4" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H9" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="1" t="s">
         <v>102</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="H10" s="4" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H10" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="1" t="s">
         <v>104</v>
       </c>
       <c r="J10" s="1">
         <v>6</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="H11" s="4" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H11" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="1" t="s">
         <v>106</v>
       </c>
       <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
-      <c r="H12" s="4" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H12" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="1" t="s">
         <v>108</v>
       </c>
       <c r="J12" s="1">
         <v>8</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
-      <c r="H13" s="4" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H13" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="1" t="s">
         <v>110</v>
       </c>
       <c r="J13" s="1">
         <v>9</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="1" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2772,32 +3078,31 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="25.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.0833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1"/>
     <col min="6" max="6" width="26.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
     <col min="8" max="8" width="44.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.8333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="23" style="1" customWidth="1"/>
-    <col min="11" max="11" width="37.0833333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="37.08203125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2819,15 +3124,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2853,7 +3158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="85.5" spans="1:12">
+    <row r="3" spans="1:12" ht="70" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2883,7 +3188,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>111</v>
       </c>
@@ -2913,32 +3218,31 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="38.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.58333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.0833333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.0833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.0833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.58203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.08203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.08203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="44.0833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="44.08203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="22" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="29.75" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2960,15 +3264,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2994,7 +3298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="171" spans="1:12">
+    <row r="3" spans="1:12" ht="168" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -3024,7 +3328,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>114</v>
       </c>
@@ -3050,7 +3354,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="1" t="s">
         <v>118</v>
       </c>
@@ -3064,7 +3368,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" s="1" t="s">
         <v>120</v>
       </c>
@@ -3078,7 +3382,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="1" t="s">
         <v>122</v>
       </c>
@@ -3092,7 +3396,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H8" s="1" t="s">
         <v>124</v>
       </c>
@@ -3106,7 +3410,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H9" s="1" t="s">
         <v>126</v>
       </c>
@@ -3120,7 +3424,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H10" s="1" t="s">
         <v>128</v>
       </c>
@@ -3138,22 +3442,21 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.875" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" customWidth="1"/>
     <col min="4" max="4" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3175,15 +3478,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3209,7 +3512,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="171" spans="1:12">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="168" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -3239,7 +3542,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>130</v>
       </c>
@@ -3262,7 +3565,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" t="s">
         <v>134</v>
       </c>
@@ -3273,7 +3576,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" t="s">
         <v>136</v>
       </c>
@@ -3288,7 +3591,7 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>